--- a/artfynd/A 28035-2023 artfynd.xlsx
+++ b/artfynd/A 28035-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4180,10 +4180,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112820989</v>
+        <v>137489867</v>
       </c>
       <c r="B28" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4191,38 +4191,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503587</v>
+        <v>503576</v>
       </c>
       <c r="R28" t="n">
-        <v>6610031</v>
+        <v>6610014</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4249,17 +4255,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4270,31 +4271,50 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820989</t>
+          <t>https://artportalen.se/Sighting/137489867</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112820991</v>
+        <v>137489868</v>
       </c>
       <c r="B29" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4302,38 +4322,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503601</v>
+        <v>503574</v>
       </c>
       <c r="R29" t="n">
-        <v>6610045</v>
+        <v>6609996</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4360,17 +4386,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4381,31 +4402,50 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820991</t>
+          <t>https://artportalen.se/Sighting/137489868</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112820997</v>
+        <v>137489869</v>
       </c>
       <c r="B30" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4413,38 +4453,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503611</v>
+        <v>503586</v>
       </c>
       <c r="R30" t="n">
-        <v>6610058</v>
+        <v>6610010</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4471,17 +4517,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4492,31 +4533,50 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820997</t>
+          <t>https://artportalen.se/Sighting/137489869</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112820998</v>
+        <v>137489870</v>
       </c>
       <c r="B31" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4524,38 +4584,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503623</v>
+        <v>503584</v>
       </c>
       <c r="R31" t="n">
-        <v>6610071</v>
+        <v>6610007</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4582,17 +4648,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4603,31 +4664,50 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820998</t>
+          <t>https://artportalen.se/Sighting/137489870</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112820999</v>
+        <v>137489871</v>
       </c>
       <c r="B32" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4635,38 +4715,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503634</v>
+        <v>503580</v>
       </c>
       <c r="R32" t="n">
-        <v>6610062</v>
+        <v>6610013</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4693,17 +4779,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4714,31 +4795,50 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820999</t>
+          <t>https://artportalen.se/Sighting/137489871</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112821000</v>
+        <v>137489872</v>
       </c>
       <c r="B33" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4746,38 +4846,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503720</v>
+        <v>503616</v>
       </c>
       <c r="R33" t="n">
-        <v>6610045</v>
+        <v>6609988</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4804,17 +4910,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4825,31 +4926,50 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821000</t>
+          <t>https://artportalen.se/Sighting/137489872</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112821001</v>
+        <v>137489873</v>
       </c>
       <c r="B34" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4857,21 +4977,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4879,16 +4999,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503710</v>
+        <v>503646</v>
       </c>
       <c r="R34" t="n">
-        <v>6610087</v>
+        <v>6609986</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4915,17 +5041,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 1 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4936,31 +5057,50 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821001</t>
+          <t>https://artportalen.se/Sighting/137489873</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112821004</v>
+        <v>137489875</v>
       </c>
       <c r="B35" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4968,38 +5108,44 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503715</v>
+        <v>503633</v>
       </c>
       <c r="R35" t="n">
-        <v>6610027</v>
+        <v>6609988</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5026,17 +5172,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5047,28 +5188,47 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821004</t>
+          <t>https://artportalen.se/Sighting/137489875</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112821007</v>
+        <v>112820989</v>
       </c>
       <c r="B36" t="n">
         <v>106813</v>
@@ -5098,7 +5258,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5107,10 +5267,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503720</v>
+        <v>503587</v>
       </c>
       <c r="R36" t="n">
-        <v>6610009</v>
+        <v>6610031</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5147,7 +5307,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5173,13 +5333,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821007</t>
+          <t>https://artportalen.se/Sighting/112820989</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112821009</v>
+        <v>112820991</v>
       </c>
       <c r="B37" t="n">
         <v>106813</v>
@@ -5209,7 +5369,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5218,10 +5378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503651</v>
+        <v>503601</v>
       </c>
       <c r="R37" t="n">
-        <v>6609980</v>
+        <v>6610045</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5258,7 +5418,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Från 0.3 till 1 m höga. Inom röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5284,13 +5444,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821009</t>
+          <t>https://artportalen.se/Sighting/112820991</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112821010</v>
+        <v>112820997</v>
       </c>
       <c r="B38" t="n">
         <v>106813</v>
@@ -5320,7 +5480,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5329,10 +5489,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503647</v>
+        <v>503611</v>
       </c>
       <c r="R38" t="n">
-        <v>6609981</v>
+        <v>6610058</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5369,7 +5529,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Från 2 till 4 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5395,13 +5555,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821010</t>
+          <t>https://artportalen.se/Sighting/112820997</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112821011</v>
+        <v>112820998</v>
       </c>
       <c r="B39" t="n">
         <v>106813</v>
@@ -5431,7 +5591,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5440,10 +5600,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503632</v>
+        <v>503623</v>
       </c>
       <c r="R39" t="n">
-        <v>6609987</v>
+        <v>6610071</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5480,7 +5640,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Från 2 till 4 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5506,13 +5666,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821011</t>
+          <t>https://artportalen.se/Sighting/112820998</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112821012</v>
+        <v>112820999</v>
       </c>
       <c r="B40" t="n">
         <v>106813</v>
@@ -5542,7 +5702,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5551,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503629</v>
+        <v>503634</v>
       </c>
       <c r="R40" t="n">
-        <v>6609986</v>
+        <v>6610062</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5591,7 +5751,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Från 0.1 till 1 m höga. I vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5617,13 +5777,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821012</t>
+          <t>https://artportalen.se/Sighting/112820999</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112821013</v>
+        <v>112821000</v>
       </c>
       <c r="B41" t="n">
         <v>106813</v>
@@ -5653,7 +5813,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5662,10 +5822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503598</v>
+        <v>503720</v>
       </c>
       <c r="R41" t="n">
-        <v>6609994</v>
+        <v>6610045</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5702,7 +5862,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Från 0.1 till 1 m höga. I vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5728,13 +5888,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821013</t>
+          <t>https://artportalen.se/Sighting/112821000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112821014</v>
+        <v>112821001</v>
       </c>
       <c r="B42" t="n">
         <v>106813</v>
@@ -5764,7 +5924,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5773,10 +5933,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503599</v>
+        <v>503710</v>
       </c>
       <c r="R42" t="n">
-        <v>6609996</v>
+        <v>6610087</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5813,7 +5973,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Från 1 till 5 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 1 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5839,13 +5999,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821014</t>
+          <t>https://artportalen.se/Sighting/112821001</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112821015</v>
+        <v>112821004</v>
       </c>
       <c r="B43" t="n">
         <v>106813</v>
@@ -5875,7 +6035,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5884,10 +6044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503578</v>
+        <v>503715</v>
       </c>
       <c r="R43" t="n">
-        <v>6610010</v>
+        <v>6610027</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5924,7 +6084,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5950,13 +6110,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821015</t>
+          <t>https://artportalen.se/Sighting/112821004</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112821017</v>
+        <v>112821007</v>
       </c>
       <c r="B44" t="n">
         <v>106813</v>
@@ -5986,7 +6146,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5995,10 +6155,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503606</v>
+        <v>503720</v>
       </c>
       <c r="R44" t="n">
-        <v>6610004</v>
+        <v>6610009</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6035,7 +6195,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6061,13 +6221,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821017</t>
+          <t>https://artportalen.se/Sighting/112821007</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112821018</v>
+        <v>112821009</v>
       </c>
       <c r="B45" t="n">
         <v>106813</v>
@@ -6097,7 +6257,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6106,10 +6266,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503618</v>
+        <v>503651</v>
       </c>
       <c r="R45" t="n">
-        <v>6610004</v>
+        <v>6609980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6146,7 +6306,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.3 till 1 m höga. Inom röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6172,13 +6332,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821018</t>
+          <t>https://artportalen.se/Sighting/112821009</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112821019</v>
+        <v>112821010</v>
       </c>
       <c r="B46" t="n">
         <v>106813</v>
@@ -6208,7 +6368,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6217,10 +6377,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503626</v>
+        <v>503647</v>
       </c>
       <c r="R46" t="n">
-        <v>6609996</v>
+        <v>6609981</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6257,7 +6417,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 2 till 4 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6283,13 +6443,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821019</t>
+          <t>https://artportalen.se/Sighting/112821010</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112821020</v>
+        <v>112821011</v>
       </c>
       <c r="B47" t="n">
         <v>106813</v>
@@ -6319,7 +6479,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6328,10 +6488,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503639</v>
+        <v>503632</v>
       </c>
       <c r="R47" t="n">
-        <v>6609995</v>
+        <v>6609987</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6368,7 +6528,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Från 0.1 till 3 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 2 till 4 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6394,13 +6554,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821020</t>
+          <t>https://artportalen.se/Sighting/112821011</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112821021</v>
+        <v>112821012</v>
       </c>
       <c r="B48" t="n">
         <v>106813</v>
@@ -6430,7 +6590,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6439,10 +6599,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503652</v>
+        <v>503629</v>
       </c>
       <c r="R48" t="n">
-        <v>6609993</v>
+        <v>6609986</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6479,7 +6639,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 1 m höga. I vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6505,13 +6665,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821021</t>
+          <t>https://artportalen.se/Sighting/112821012</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112821022</v>
+        <v>112821013</v>
       </c>
       <c r="B49" t="n">
         <v>106813</v>
@@ -6541,7 +6701,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6550,10 +6710,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503627</v>
+        <v>503598</v>
       </c>
       <c r="R49" t="n">
-        <v>6610018</v>
+        <v>6609994</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6590,7 +6750,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 1 m höga. I vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6616,13 +6776,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821022</t>
+          <t>https://artportalen.se/Sighting/112821013</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112821023</v>
+        <v>112821014</v>
       </c>
       <c r="B50" t="n">
         <v>106813</v>
@@ -6652,7 +6812,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6661,10 +6821,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503568</v>
+        <v>503599</v>
       </c>
       <c r="R50" t="n">
-        <v>6610017</v>
+        <v>6609996</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6701,7 +6861,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 1 till 5 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6727,13 +6887,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821023</t>
+          <t>https://artportalen.se/Sighting/112821014</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112821025</v>
+        <v>112821015</v>
       </c>
       <c r="B51" t="n">
         <v>106813</v>
@@ -6763,7 +6923,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6772,10 +6932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503572</v>
+        <v>503578</v>
       </c>
       <c r="R51" t="n">
-        <v>6610007</v>
+        <v>6610010</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6812,7 +6972,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6838,33 +6998,33 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821025</t>
+          <t>https://artportalen.se/Sighting/112821015</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112821024</v>
+        <v>112821017</v>
       </c>
       <c r="B52" t="n">
-        <v>106156</v>
+        <v>106813</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6872,17 +7032,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503576</v>
+        <v>503606</v>
       </c>
       <c r="R52" t="n">
-        <v>6610009</v>
+        <v>6610004</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6917,6 +7081,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6940,33 +7109,33 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112821024</t>
+          <t>https://artportalen.se/Sighting/112821017</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112820988</v>
+        <v>112821018</v>
       </c>
       <c r="B53" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6976,7 +7145,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6985,10 +7154,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503584</v>
+        <v>503618</v>
       </c>
       <c r="R53" t="n">
-        <v>6610029</v>
+        <v>6610004</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7023,6 +7192,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7046,33 +7220,33 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820988</t>
+          <t>https://artportalen.se/Sighting/112821018</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112820992</v>
+        <v>112821019</v>
       </c>
       <c r="B54" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7082,7 +7256,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7091,10 +7265,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503606</v>
+        <v>503626</v>
       </c>
       <c r="R54" t="n">
-        <v>6610046</v>
+        <v>6609996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7129,6 +7303,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7152,33 +7331,33 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820992</t>
+          <t>https://artportalen.se/Sighting/112821019</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112820996</v>
+        <v>112821020</v>
       </c>
       <c r="B55" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7188,7 +7367,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7197,10 +7376,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503611</v>
+        <v>503639</v>
       </c>
       <c r="R55" t="n">
-        <v>6610061</v>
+        <v>6609995</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7235,6 +7414,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 3 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7258,51 +7442,55 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820996</t>
+          <t>https://artportalen.se/Sighting/112821020</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112820993</v>
+        <v>112821021</v>
       </c>
       <c r="B56" t="n">
-        <v>101326</v>
+        <v>106813</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503612</v>
+        <v>503652</v>
       </c>
       <c r="R56" t="n">
-        <v>6610054</v>
+        <v>6609993</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7337,6 +7525,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7359,6 +7552,861 @@
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821021</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>112821022</v>
+      </c>
+      <c r="B57" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>503627</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6610018</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821022</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>112821023</v>
+      </c>
+      <c r="B58" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>503568</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6610017</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821023</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>112821025</v>
+      </c>
+      <c r="B59" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>503572</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6610007</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>112821024</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>503576</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6610009</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821024</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>112820988</v>
+      </c>
+      <c r="B61" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>503584</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6610029</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820988</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>112820992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>503606</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6610046</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820992</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>112820996</v>
+      </c>
+      <c r="B63" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>503611</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6610061</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820996</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>112820993</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>503612</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6610054</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112820993</t>
         </is>
@@ -7421,6 +8469,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
